--- a/Frontend/public/templates/students-import-template.xlsx
+++ b/Frontend/public/templates/students-import-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -422,7 +422,7 @@
         <v>Địa chỉ</v>
       </c>
       <c r="H1" t="str">
-        <v>Ngành học</v>
+        <v>Mã chương trình đào tạo</v>
       </c>
       <c r="I1" t="str">
         <v>Khóa học</v>
@@ -451,7 +451,7 @@
         <v>Địa chỉ mẫu</v>
       </c>
       <c r="H2" t="str">
-        <v>Ngành học mẫu</v>
+        <v>CTDT001</v>
       </c>
       <c r="I2" t="str">
         <v>0</v>
